--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T03:56:06Z by SETUP | data b66cf958da23f2cb</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T03:56:06Z by SETUP | data b66cf958da23f2cb</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T03:56:06Z by SETUP | data b66cf958da23f2cb</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D218"/>
+  <dimension ref="A1:D219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T03:56:06Z by SETUP | data b66cf958da23f2cb</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
         </is>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ER-03.07</t>
+          <t>ER-03.02</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -11321,14 +11321,14 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>cites TS EN 590: in the register</t>
+          <t>cites ISO 6976: in the register</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>ER-03.08</t>
+          <t>ER-03.07</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>cites NFPA 11: in the register</t>
+          <t>cites TS EN 590: in the register</t>
         </is>
       </c>
     </row>
@@ -11365,14 +11365,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>cites NFPA 30: in the register</t>
+          <t>cites NFPA 11: in the register</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>ER-04.07</t>
+          <t>ER-03.08</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -11387,14 +11387,14 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>cites Grid Code: in the register</t>
+          <t>cites NFPA 30: in the register</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>ER-05.02</t>
+          <t>ER-04.07</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -11409,14 +11409,14 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>cites EN 1822: in the register</t>
+          <t>cites Grid Code: in the register</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ER-05.06</t>
+          <t>ER-05.02</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -11431,14 +11431,14 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 62443: in the register</t>
+          <t>cites EN 1822: in the register</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ER-06.02</t>
+          <t>ER-05.06</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>cites ASME I: in the register</t>
+          <t>cites IEC 62443: in the register</t>
         </is>
       </c>
     </row>
@@ -11475,7 +11475,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>cites EN 12952: in the register</t>
+          <t>cites ASME I: in the register</t>
         </is>
       </c>
     </row>
@@ -11497,14 +11497,14 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>cites PED 2014/68/EU: in the register</t>
+          <t>cites EN 12952: in the register</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ER-06.05</t>
+          <t>ER-06.02</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -11519,14 +11519,14 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>cites EN 12952-3: in the register</t>
+          <t>cites PED 2014/68/EU: in the register</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>ER-06.06</t>
+          <t>ER-06.05</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -11541,14 +11541,14 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>cites EN 15259: in the register</t>
+          <t>cites EN 12952-3: in the register</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>ER-07.07</t>
+          <t>ER-06.06</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -11563,14 +11563,14 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>cites HEI: in the register</t>
+          <t>cites EN 15259: in the register</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>ER-07.08</t>
+          <t>ER-07.07</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>cites ASME PTC 12.2: in the register</t>
+          <t>cites HEI: in the register</t>
         </is>
       </c>
     </row>
@@ -11607,14 +11607,14 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>cites HEI: in the register</t>
+          <t>cites ASME PTC 12.2: in the register</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>ER-07.09</t>
+          <t>ER-07.08</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -11636,7 +11636,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>ER-07.10</t>
+          <t>ER-07.09</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -11658,7 +11658,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ER-09.03</t>
+          <t>ER-07.10</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -11673,14 +11673,14 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>cites VGB-S-010: in the register</t>
+          <t>cites HEI: in the register</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ER-10.05</t>
+          <t>ER-09.03</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -11695,14 +11695,14 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>cites NFPA 850: in the register</t>
+          <t>cites VGB-S-010: in the register</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ER-11.02</t>
+          <t>ER-10.05</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 60034: in the register</t>
+          <t>cites NFPA 850: in the register</t>
         </is>
       </c>
     </row>
@@ -11739,14 +11739,14 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>cites IEC/IEEE 62271-37-013: in the register</t>
+          <t>cites IEC 60034: in the register</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>ER-11.03</t>
+          <t>ER-11.02</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -11761,14 +11761,14 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 60076: in the register</t>
+          <t>cites IEC/IEEE 62271-37-013: in the register</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ER-11.07</t>
+          <t>ER-11.03</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 62305: in the register</t>
+          <t>cites IEC 60076: in the register</t>
         </is>
       </c>
     </row>
@@ -11805,14 +11805,14 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>cites IEEE 80: in the register</t>
+          <t>cites IEC 62305: in the register</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>ER-12.03</t>
+          <t>ER-11.07</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -11827,14 +11827,14 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 61511: in the register</t>
+          <t>cites IEEE 80: in the register</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>ER-12.04</t>
+          <t>ER-12.03</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -11849,14 +11849,14 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>cites EN 14181: in the register</t>
+          <t>cites IEC 61511: in the register</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>ER-12.05</t>
+          <t>ER-12.04</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -11871,14 +11871,14 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>cites ASME PTC 46: in the register</t>
+          <t>cites EN 14181: in the register</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>ER-12.07</t>
+          <t>ER-12.05</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -11893,14 +11893,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 62443: in the register</t>
+          <t>cites ASME PTC 46: in the register</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>ER-13.03</t>
+          <t>ER-12.07</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>cites EN 1993: in the register</t>
+          <t>cites IEC 62443: in the register</t>
         </is>
       </c>
     </row>
@@ -11937,14 +11937,14 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>cites EN ISO 1461: in the register</t>
+          <t>cites EN 1993: in the register</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>ER-13.04</t>
+          <t>ER-13.03</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>cites EN 1992: in the register</t>
+          <t>cites EN ISO 1461: in the register</t>
         </is>
       </c>
     </row>
@@ -11981,14 +11981,14 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>cites TS 500: in the register</t>
+          <t>cites EN 1992: in the register</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>ER-14.01</t>
+          <t>ER-13.04</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -12003,14 +12003,14 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>cites Law 2872: in the register</t>
+          <t>cites TS 500: in the register</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>ER-14.05</t>
+          <t>ER-14.01</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>cites ISO 45001: in the register</t>
+          <t>cites Law 2872: in the register</t>
         </is>
       </c>
     </row>
@@ -12047,14 +12047,14 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>cites Law 6331: in the register</t>
+          <t>cites ISO 45001: in the register</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>ER-14.06</t>
+          <t>ER-14.05</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -12069,14 +12069,14 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>cites IEC 60079-10-1: in the register</t>
+          <t>cites Law 6331: in the register</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>ER-15.01</t>
+          <t>ER-14.06</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -12091,14 +12091,14 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>cites ISO 9001: in the register</t>
+          <t>cites IEC 60079-10-1: in the register</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>ER-15.04</t>
+          <t>ER-15.01</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -12113,14 +12113,14 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>cites EN 10204: in the register</t>
+          <t>cites ISO 9001: in the register</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>ER-15.05</t>
+          <t>ER-15.04</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>cites ASME IX: in the register</t>
+          <t>cites EN 10204: in the register</t>
         </is>
       </c>
     </row>
@@ -12157,14 +12157,14 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>cites EN ISO 15614: in the register</t>
+          <t>cites ASME IX: in the register</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>ER-16.04</t>
+          <t>ER-15.05</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -12179,14 +12179,14 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>cites ASME PTC 46: in the register</t>
+          <t>cites EN ISO 15614: in the register</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>ER-18.02</t>
+          <t>ER-16.04</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -12201,19 +12201,19 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>cites Grid Code: in the register</t>
+          <t>cites ASME PTC 46: in the register</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0025</t>
+          <t>ER-18.02</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>ER coverage</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -12223,14 +12223,14 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>ATEX 2014/34/EU: agreed by IEC, IEPC, OWNER</t>
+          <t>cites Grid Code: in the register</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0012</t>
+          <t>REF-CONS-0025</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -12245,14 +12245,14 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Construction OHS Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>ATEX 2014/34/EU: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0002</t>
+          <t>REF-CONS-0012</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -12267,14 +12267,14 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>EIA Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Construction OHS Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0022</t>
+          <t>REF-CONS-0002</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -12289,14 +12289,14 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Earthing Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>EIA Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0003</t>
+          <t>REF-CONS-0022</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -12311,14 +12311,14 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Earthing Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0014</t>
+          <t>REF-CONS-0003</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -12333,14 +12333,14 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Explosive Atmospheres Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Env. Permit Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0016</t>
+          <t>REF-CONS-0014</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -12355,14 +12355,14 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Fire Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Explosive Atmospheres Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0021</t>
+          <t>REF-CONS-0016</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -12377,14 +12377,14 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Heavy Current Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Fire Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0005</t>
+          <t>REF-CONS-0021</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -12399,14 +12399,14 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>LCP Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Heavy Current Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0028</t>
+          <t>REF-CONS-0005</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -12421,14 +12421,14 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Law 167: agreed by IEPC, OWNER</t>
+          <t>LCP Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0026</t>
+          <t>REF-CONS-0028</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -12443,14 +12443,14 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Law 2863: agreed by IEPC, OWNER</t>
+          <t>Law 167: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0001</t>
+          <t>REF-CONS-0026</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -12465,14 +12465,14 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Law 2872: agreed by IEC, IEPC, OWNER</t>
+          <t>Law 2863: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0029</t>
+          <t>REF-CONS-0001</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -12487,14 +12487,14 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Law 2918: agreed by IEPC, OWNER</t>
+          <t>Law 2872: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0015</t>
+          <t>REF-CONS-0029</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -12509,14 +12509,14 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Law 3194: agreed by IEC, IEPC, OWNER</t>
+          <t>Law 2918: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0018</t>
+          <t>REF-CONS-0015</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -12531,14 +12531,14 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Law 3621: agreed by IEPC, OWNER</t>
+          <t>Law 3194: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0027</t>
+          <t>REF-CONS-0018</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -12553,14 +12553,14 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Law 4646: agreed by IEPC, OWNER</t>
+          <t>Law 3621: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0011</t>
+          <t>REF-CONS-0027</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -12575,14 +12575,14 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Law 6331: agreed by IEC, IEPC, OWNER</t>
+          <t>Law 4646: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0019</t>
+          <t>REF-CONS-0011</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -12597,14 +12597,14 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Law 6446: agreed by IEPC, OWNER</t>
+          <t>Law 6331: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0030</t>
+          <t>REF-CONS-0019</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -12619,14 +12619,14 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Law 7381: agreed by IEC, IEPC, OWNER</t>
+          <t>Law 6446: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0024</t>
+          <t>REF-CONS-0030</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -12641,14 +12641,14 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Machinery Directive 2006/42/EC: agreed by IEC, IEPC, OWNER</t>
+          <t>Law 7381: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0010</t>
+          <t>REF-CONS-0024</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -12663,14 +12663,14 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Major Accident Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Machinery Directive 2006/42/EC: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0007</t>
+          <t>REF-CONS-0010</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -12685,14 +12685,14 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Noise Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Major Accident Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0023</t>
+          <t>REF-CONS-0007</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -12707,14 +12707,14 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>PED 2014/68/EU: agreed by IEC, IEPC, OWNER</t>
+          <t>Noise Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0004</t>
+          <t>REF-CONS-0023</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -12729,14 +12729,14 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>SKHKKY: agreed by IEC, IEPC, OWNER</t>
+          <t>PED 2014/68/EU: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0009</t>
+          <t>REF-CONS-0004</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -12751,14 +12751,14 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Soil Regulation: agreed by IEPC, OWNER</t>
+          <t>SKHKKY: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0017</t>
+          <t>REF-CONS-0009</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -12773,14 +12773,14 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>TBDY 2018: agreed by IEC, IEPC, OWNER</t>
+          <t>Soil Regulation: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0006</t>
+          <t>REF-CONS-0017</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -12795,14 +12795,14 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>WPCR: agreed by IEPC, OWNER</t>
+          <t>TBDY 2018: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0008</t>
+          <t>REF-CONS-0006</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -12817,14 +12817,14 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Waste Regulation: agreed by IEPC, OWNER</t>
+          <t>WPCR: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0013</t>
+          <t>REF-CONS-0008</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -12839,14 +12839,14 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Work Equipment Regulation: agreed by IEC, IEPC, OWNER</t>
+          <t>Waste Regulation: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0020</t>
+          <t>REF-CONS-0013</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -12861,14 +12861,14 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Grid Code: agreed by IEC, IEPC, OWNER</t>
+          <t>Work Equipment Regulation: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0093</t>
+          <t>REF-CONS-0020</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -12883,14 +12883,14 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>ACI 351.3R: agreed by IEPC, OWNER</t>
+          <t>Grid Code: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0066</t>
+          <t>REF-CONS-0093</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -12905,14 +12905,14 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>API 650: agreed by IEPC, OWNER</t>
+          <t>ACI 351.3R: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0060</t>
+          <t>REF-CONS-0066</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -12927,14 +12927,14 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>ASME B16.25: agreed by IEC, IEPC, OWNER</t>
+          <t>API 650: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0061</t>
+          <t>REF-CONS-0060</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -12949,14 +12949,14 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>ASME B16.34: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME B16.25: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0059</t>
+          <t>REF-CONS-0061</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -12971,14 +12971,14 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>ASME B16.5: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME B16.34: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0055</t>
+          <t>REF-CONS-0059</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -12993,14 +12993,14 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>ASME B31.1: agreed by IEPC, OWNER</t>
+          <t>ASME B16.5: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0056</t>
+          <t>REF-CONS-0055</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -13015,14 +13015,14 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>ASME B31.3: agreed by IEPC, OWNER</t>
+          <t>ASME B31.1: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0057</t>
+          <t>REF-CONS-0056</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -13037,14 +13037,14 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>ASME B31.8: agreed by IEPC, OWNER</t>
+          <t>ASME B31.3: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>REF-SETUP-0002</t>
+          <t>REF-CONS-0057</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -13059,14 +13059,14 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>ASME B36.10M: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME B31.8: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0046</t>
+          <t>REF-SETUP-0002</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -13081,14 +13081,14 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>ASME PTC 12.2: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME B36.10M: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0034</t>
+          <t>REF-CONS-0046</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -13103,14 +13103,14 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>ASME PTC 22: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME PTC 12.2: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0044</t>
+          <t>REF-CONS-0034</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -13125,14 +13125,14 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>ASME PTC 4.4: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME PTC 22: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0050</t>
+          <t>REF-CONS-0044</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -13147,14 +13147,14 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>ASME PTC 46: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME PTC 4.4: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0036</t>
+          <t>REF-CONS-0050</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -13169,14 +13169,14 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>ASME PTC 6: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME PTC 46: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0042</t>
+          <t>REF-CONS-0036</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -13191,14 +13191,14 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>ASME Section I: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME PTC 6: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0063</t>
+          <t>REF-CONS-0042</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -13213,14 +13213,14 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>ASME Section IX: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME Section I: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0062</t>
+          <t>REF-CONS-0063</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -13235,14 +13235,14 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>ASME Section VIII Div. 1: agreed by IEPC, OWNER</t>
+          <t>ASME Section IX: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0065</t>
+          <t>REF-CONS-0062</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -13257,14 +13257,14 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>EN 10204: agreed by IEC, IEPC, OWNER</t>
+          <t>ASME Section VIII Div. 1: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0058</t>
+          <t>REF-CONS-0065</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -13279,14 +13279,14 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>EN 12186: agreed by IEPC, OWNER</t>
+          <t>EN 10204: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0043</t>
+          <t>REF-CONS-0058</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -13301,14 +13301,14 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>EN 12952: agreed by IEC, IEPC, OWNER</t>
+          <t>EN 12186: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0072</t>
+          <t>REF-CONS-0043</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -13323,14 +13323,14 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>EN 13001: agreed by IEPC, OWNER</t>
+          <t>EN 12952: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0084</t>
+          <t>REF-CONS-0072</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -13345,14 +13345,14 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>EN 14181: agreed by IEPC, OWNER</t>
+          <t>EN 13001: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0086</t>
+          <t>REF-CONS-0084</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -13367,14 +13367,14 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>EN 15259: agreed by IEPC, OWNER</t>
+          <t>EN 14181: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0085</t>
+          <t>REF-CONS-0086</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -13389,14 +13389,14 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>EN 15267-3: agreed by IEPC, OWNER</t>
+          <t>EN 15259: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0047</t>
+          <t>REF-CONS-0085</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
@@ -13411,14 +13411,14 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>EN 1822: agreed by IEC, IEPC, OWNER</t>
+          <t>EN 15267-3: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0087</t>
+          <t>REF-CONS-0047</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -13433,14 +13433,14 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>EN 1990: agreed by IEPC, OWNER</t>
+          <t>EN 1822: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0088</t>
+          <t>REF-CONS-0087</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -13455,14 +13455,14 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>EN 1992: agreed by IEPC, OWNER</t>
+          <t>EN 1990: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0090</t>
+          <t>REF-CONS-0088</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
@@ -13477,14 +13477,14 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>EN 1993: agreed by IEPC, OWNER</t>
+          <t>EN 1992: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0091</t>
+          <t>REF-CONS-0090</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -13499,14 +13499,14 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>EN ISO 1461: agreed by IEPC, OWNER</t>
+          <t>EN 1993: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0064</t>
+          <t>REF-CONS-0091</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
@@ -13521,14 +13521,14 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>EN ISO 15614: agreed by IEC, IEPC, OWNER</t>
+          <t>EN ISO 1461: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0045</t>
+          <t>REF-CONS-0064</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -13543,14 +13543,14 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>HEI 2629: agreed by IEC, IEPC, OWNER</t>
+          <t>EN ISO 15614: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0053</t>
+          <t>REF-CONS-0045</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -13565,14 +13565,14 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>IAPWS TGD: agreed by IEC, IEPC, OWNER</t>
+          <t>HEI 2629: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0052</t>
+          <t>REF-CONS-0053</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -13587,14 +13587,14 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>IAPWS-IF97: agreed by IEC, IEPC, OWNER</t>
+          <t>IAPWS TGD: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0037</t>
+          <t>REF-CONS-0052</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
@@ -13609,14 +13609,14 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>IEC 60034-1: agreed by IEC, IEPC, OWNER</t>
+          <t>IAPWS-IF97: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0035</t>
+          <t>REF-CONS-0037</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -13631,14 +13631,14 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>IEC 60045-1: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60034-1: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0040</t>
+          <t>REF-CONS-0035</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -13653,14 +13653,14 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>IEC 60076: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60045-1: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0083</t>
+          <t>REF-CONS-0040</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
@@ -13675,14 +13675,14 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>IEC 60079-10-1: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60076: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0077</t>
+          <t>REF-CONS-0083</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -13697,14 +13697,14 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>IEC 60364: agreed by IEPC, OWNER</t>
+          <t>IEC 60079-10-1: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0080</t>
+          <t>REF-CONS-0077</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -13719,14 +13719,14 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>IEC 60815: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60364: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0075</t>
+          <t>REF-CONS-0080</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
@@ -13741,14 +13741,14 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>IEC 60909: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60815: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0081</t>
+          <t>REF-CONS-0075</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -13763,14 +13763,14 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>IEC 61511: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60909: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0076</t>
+          <t>REF-CONS-0081</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
@@ -13785,14 +13785,14 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>IEC 61850: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 61511: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0073</t>
+          <t>REF-CONS-0076</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -13807,14 +13807,14 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>IEC 61936-1: agreed by IEPC, OWNER</t>
+          <t>IEC 61850: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0074</t>
+          <t>REF-CONS-0073</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -13829,14 +13829,14 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>IEC 62271-203: agreed by IEPC, OWNER</t>
+          <t>IEC 61936-1: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0079</t>
+          <t>REF-CONS-0074</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
@@ -13851,14 +13851,14 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>IEC 62305: agreed by IEPC, OWNER</t>
+          <t>IEC 62271-203: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0082</t>
+          <t>REF-CONS-0079</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -13873,14 +13873,14 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>IEC 62443: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 62305: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0041</t>
+          <t>REF-CONS-0082</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
@@ -13895,14 +13895,14 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>IEC 62770: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 62443: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0038</t>
+          <t>REF-CONS-0041</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -13917,14 +13917,14 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>IEC/IEEE 62271-37-013: agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 62770: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0078</t>
+          <t>REF-CONS-0038</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -13939,14 +13939,14 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>IEEE 80: agreed by IEPC, OWNER</t>
+          <t>IEC/IEEE 62271-37-013: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0039</t>
+          <t>REF-CONS-0078</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -13961,14 +13961,14 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>IEEE C37.102: agreed by IEC, IEPC, OWNER</t>
+          <t>IEEE 80: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0033</t>
+          <t>REF-CONS-0039</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -13983,14 +13983,14 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>ISO 10494: agreed by IEC, IEPC, OWNER</t>
+          <t>IEEE C37.102: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0092</t>
+          <t>REF-CONS-0033</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -14005,14 +14005,14 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>ISO 12944-2: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 10494: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>REF-OWNR-0001</t>
+          <t>REF-CONS-0092</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -14027,14 +14027,14 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>ISO 14001: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 12944-2: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0097</t>
+          <t>REF-OWNR-0001</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -14049,14 +14049,14 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>ISO 20816-2: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 14001: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0031</t>
+          <t>REF-CONS-0097</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -14071,14 +14071,14 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>ISO 21789: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 20816-2: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0032</t>
+          <t>REF-CONS-0031</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -14093,14 +14093,14 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>ISO 3977-3: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 21789: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0095</t>
+          <t>REF-CONS-0032</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
@@ -14115,14 +14115,14 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>ISO 45001: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 3977-3: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0051</t>
+          <t>REF-CONS-0095</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
@@ -14137,14 +14137,14 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>ISO 6976: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 45001: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0094</t>
+          <t>REF-CONS-0051</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
@@ -14159,14 +14159,14 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>ISO 9001: agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 6976: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0068</t>
+          <t>REF-CONS-0094</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
@@ -14181,14 +14181,14 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>NFPA 11: agreed by IEPC, OWNER</t>
+          <t>ISO 9001: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0048</t>
+          <t>REF-CONS-0068</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -14203,14 +14203,14 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>NFPA 12: agreed by IEC, IEPC, OWNER</t>
+          <t>NFPA 11: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0070</t>
+          <t>REF-CONS-0048</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
@@ -14225,14 +14225,14 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>NFPA 20: agreed by IEPC, OWNER</t>
+          <t>NFPA 12: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0067</t>
+          <t>REF-CONS-0070</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
@@ -14247,14 +14247,14 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>NFPA 30: agreed by IEPC, OWNER</t>
+          <t>NFPA 20: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0071</t>
+          <t>REF-CONS-0067</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -14269,14 +14269,14 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>NFPA 72: agreed by IEPC, OWNER</t>
+          <t>NFPA 30: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0049</t>
+          <t>REF-CONS-0071</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -14291,14 +14291,14 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>NFPA 85: agreed by IEC, IEPC, OWNER</t>
+          <t>NFPA 72: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0069</t>
+          <t>REF-CONS-0049</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -14313,14 +14313,14 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>NFPA 850: agreed by IEC, IEPC, OWNER</t>
+          <t>NFPA 85: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0089</t>
+          <t>REF-CONS-0069</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -14335,14 +14335,14 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>TS 500: agreed by IEPC, OWNER</t>
+          <t>NFPA 850: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0096</t>
+          <t>REF-CONS-0089</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -14357,14 +14357,14 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>TS EN 590: agreed by IEPC, OWNER</t>
+          <t>TS 500: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>REF-CONS-0054</t>
+          <t>REF-CONS-0096</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -14379,14 +14379,14 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>VGB-S-010: agreed by IEC, IEPC, OWNER</t>
+          <t>TS EN 590: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>REF-SETUP-0001</t>
+          <t>REF-CONS-0054</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -14401,19 +14401,19 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>AVEVA class library 1.0.1: agreed by IEPC, OWNER</t>
+          <t>VGB-S-010: agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>PMT-001</t>
+          <t>REF-SETUP-0001</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Law 2872, EIA Regulation</t>
+          <t>AVEVA class library 1.0.1: agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -14445,19 +14445,19 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>Law 2872, EIA Regulation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>PMT-002</t>
+          <t>PMT-001</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Law 6446</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
@@ -14489,19 +14489,19 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>Law 6446</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>PMT-003</t>
+          <t>PMT-002</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
@@ -14511,7 +14511,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Law 6446, Grid Code</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C156" s="6" t="inlineStr">
@@ -14533,19 +14533,19 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>Law 6446, Grid Code</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>PMT-004</t>
+          <t>PMT-003</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Law 6446, Grid Code</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-03-15 + 90 d = 2028-06-13; needed 2028-07-15: float 32 d</t>
+          <t>Law 6446, Grid Code</t>
         </is>
       </c>
     </row>
@@ -14589,7 +14589,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
@@ -14599,19 +14599,19 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2028-03-15 + 90 d = 2028-06-13; needed 2028-07-15: float 32 d</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>PMT-005</t>
+          <t>PMT-004</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C160" s="6" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Law 3194, TBDY 2018, Fire Regulation</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C161" s="6" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+          <t>Law 3194, TBDY 2018, Fire Regulation</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C162" s="6" t="inlineStr">
@@ -14665,19 +14665,19 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>PMT-006</t>
+          <t>PMT-005</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C163" s="6" t="inlineStr">
@@ -14687,7 +14687,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Law 3621, EIA Regulation</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14699,7 +14699,7 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C164" s="6" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-02 + 180 d = 2027-05-01; needed 2027-10-01: float 153 d</t>
+          <t>Law 3621, EIA Regulation</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14721,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C165" s="6" t="inlineStr">
@@ -14731,19 +14731,19 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2026-11-02 + 180 d = 2027-05-01; needed 2027-10-01: float 153 d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>PMT-007</t>
+          <t>PMT-006</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Law 3621</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C167" s="6" t="inlineStr">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-04-01 + 180 d = 2027-09-28; needed 2027-11-01: float 34 d</t>
+          <t>Law 3621</t>
         </is>
       </c>
     </row>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
@@ -14797,19 +14797,19 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2027-04-01 + 180 d = 2027-09-28; needed 2027-11-01: float 34 d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>PMT-008</t>
+          <t>PMT-007</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Law 3621</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14831,7 +14831,7 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
@@ -14841,7 +14841,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-15 + 30 d = 2027-10-15; needed 2027-11-01: float 17 d</t>
+          <t>Law 3621</t>
         </is>
       </c>
     </row>
@@ -14853,7 +14853,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
@@ -14863,19 +14863,19 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2027-09-15 + 30 d = 2027-10-15; needed 2027-11-01: float 17 d</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>PMT-009</t>
+          <t>PMT-008</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C172" s="6" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Law 2918</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-01 + 30 d = 2027-10-01; needed 2027-11-01: float 31 d</t>
+          <t>Law 2918</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -14929,19 +14929,19 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2027-09-01 + 30 d = 2027-10-01; needed 2027-11-01: float 31 d</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>PMT-010</t>
+          <t>PMT-009</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Law 6331, Construction OHS Regulation</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -14963,17 +14963,17 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C176" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-02 + 10 d = 2026-11-12; needed 2026-11-16: float 4 d</t>
+          <t>Law 6331, Construction OHS Regulation</t>
         </is>
       </c>
     </row>
@@ -14985,29 +14985,29 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
-        </is>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2026-11-02 + 10 d = 2026-11-12; needed 2026-11-16: float 4 d</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>PMT-011</t>
+          <t>PMT-010</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C178" s="6" t="inlineStr">
@@ -15017,7 +15017,7 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Noise Regulation, EIA Regulation</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15029,7 +15029,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C179" s="6" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-12-01 + 30 d = 2026-12-31; needed 2027-01-15: float 15 d</t>
+          <t>Noise Regulation, EIA Regulation</t>
         </is>
       </c>
     </row>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
@@ -15061,19 +15061,19 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2026-12-01 + 30 d = 2026-12-31; needed 2027-01-15: float 15 d</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>PMT-012</t>
+          <t>PMT-011</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Law 167</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+          <t>Law 167</t>
         </is>
       </c>
     </row>
@@ -15117,7 +15117,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
@@ -15127,19 +15127,19 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>PMT-013</t>
+          <t>PMT-012</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Law 7381</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15161,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-15 + 60 d = 2027-11-14; needed 2027-12-01: float 17 d</t>
+          <t>Law 7381</t>
         </is>
       </c>
     </row>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
@@ -15193,19 +15193,19 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2027-09-15 + 60 d = 2027-11-14; needed 2027-12-01: float 17 d</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>PMT-014</t>
+          <t>PMT-013</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C187" s="6" t="inlineStr">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Law 4646</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
@@ -15237,7 +15237,7 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-03-15 + 120 d = 2028-07-13; needed 2028-08-15: float 33 d</t>
+          <t>Law 4646</t>
         </is>
       </c>
     </row>
@@ -15249,7 +15249,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
@@ -15259,19 +15259,19 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2028-03-15 + 120 d = 2028-07-13; needed 2028-08-15: float 33 d</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>PMT-015</t>
+          <t>PMT-014</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Major Accident Regulation</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-08-15 + 60 d = 2028-10-14; needed 2028-11-01: float 18 d</t>
+          <t>Major Accident Regulation</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
@@ -15325,19 +15325,19 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2028-08-15 + 60 d = 2028-10-14; needed 2028-11-01: float 18 d</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>PMT-016</t>
+          <t>PMT-015</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Work Equipment Regulation, PED 2014/68/EU</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
@@ -15369,7 +15369,7 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-06-15 + 14 d = 2028-06-29; needed 2028-08-01: float 33 d</t>
+          <t>Work Equipment Regulation, PED 2014/68/EU</t>
         </is>
       </c>
     </row>
@@ -15381,7 +15381,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -15391,19 +15391,19 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2028-06-15 + 14 d = 2028-06-29; needed 2028-08-01: float 33 d</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>PMT-017</t>
+          <t>PMT-016</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, SKHKKY</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-07-15 + 45 d = 2028-08-29; needed 2028-10-02: float 34 d</t>
+          <t>Env. Permit Regulation, SKHKKY</t>
         </is>
       </c>
     </row>
@@ -15447,7 +15447,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
@@ -15457,19 +15457,19 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2028-07-15 + 45 d = 2028-08-29; needed 2028-10-02: float 34 d</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>PMT-018</t>
+          <t>PMT-017</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-08-15 + 30 d = 2028-09-14; needed 2028-10-02: float 18 d</t>
+          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -15523,19 +15523,19 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2028-08-15 + 30 d = 2028-09-14; needed 2028-10-02: float 18 d</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>PMT-019</t>
+          <t>PMT-018</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C203" s="6" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-03-01 + 90 d = 2029-05-30; needed 2029-07-04: float 35 d</t>
+          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
@@ -15589,19 +15589,19 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2029-03-01 + 90 d = 2029-05-30; needed 2029-07-04: float 35 d</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>PMT-020</t>
+          <t>PMT-019</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C205" s="6" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Law 3194, Fire Regulation</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C206" s="6" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-05-15 + 30 d = 2029-06-14; needed 2029-07-04: float 20 d</t>
+          <t>Law 3194, Fire Regulation</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C207" s="6" t="inlineStr">
@@ -15655,19 +15655,19 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2029-05-15 + 30 d = 2029-06-14; needed 2029-07-04: float 20 d</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>PMT-021</t>
+          <t>PMT-020</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C208" s="6" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Grid Code</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15689,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
@@ -15699,7 +15699,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-01-02 + 60 d = 2029-03-03; needed 2029-07-04: float 123 d</t>
+          <t>Grid Code</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -15721,19 +15721,19 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>apply 2029-01-02 + 60 d = 2029-03-03; needed 2029-07-04: float 123 d</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>PMT-022</t>
+          <t>PMT-021</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>WPCR</t>
+          <t>agreed by IEC, IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15755,7 +15755,7 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
@@ -15765,19 +15765,19 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>WPCR</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>PMT-023</t>
+          <t>PMT-022</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Law 6446</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-12-15 + 60 d = 2027-02-13; needed 2027-03-15: float 30 d</t>
+          <t>Law 6446</t>
         </is>
       </c>
     </row>
@@ -15821,7 +15821,7 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>timing</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
@@ -15831,19 +15831,19 @@
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>apply 2026-12-15 + 60 d = 2027-02-13; needed 2027-03-15: float 30 d</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>PMT-025</t>
+          <t>PMT-023</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -15853,7 +15853,7 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Law 2863</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
@@ -15865,17 +15865,17 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C217" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>no lead time: procedural, needed from 2026-11-16</t>
+          <t>Law 2863</t>
         </is>
       </c>
     </row>
@@ -15887,15 +15887,37 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C218" s="7" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>no lead time: procedural, needed from 2026-11-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>PMT-025</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
           <t>agreement</t>
         </is>
       </c>
-      <c r="C218" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D218" s="5" t="inlineStr">
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
         <is>
           <t>agreed by IEPC, OWNER</t>
         </is>

--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T15:04:36Z by SETUP | data 3e839f9140767e6b</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
         </is>
       </c>
     </row>

--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T17:23:32Z by SETUP | data 4e7f6cc86d38a5af</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
         </is>
       </c>
     </row>

--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T18:13:43Z by SETUP | data 7a1769b572d55212</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
         </is>
       </c>
     </row>

--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
         </is>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
         </is>
       </c>
     </row>
@@ -10690,7 +10690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-28T19:01:39Z by EPCE | data a453b27ac859f0b5</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
         </is>
       </c>
     </row>

--- a/output/standards_register/ALP_codes_standards_permits_register.xlsx
+++ b/output/standards_register/ALP_codes_standards_permits_register.xlsx
@@ -47,7 +47,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
     <fill>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +104,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -466,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,7 +506,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T03:51:00Z by EPCE | data e9668cfc01fd011a</t>
         </is>
       </c>
     </row>
@@ -8381,6 +8389,3801 @@
           <t>TQ-033</t>
         </is>
       </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0045</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>regulation</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Turkish regulations on noise at work and on chemical agents at work</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Calisanlarin Gurultu ile Ilgili Risklerden Korunmasi Hakkinda Yonetmelik; Kimyasal Maddelerle Calisirken Saglik ve Guvenlik Onlemleri Hakkinda Yonetmelik</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>Occupational exposure limits used in HS-DBR-0001 section 6</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P105" s="4" t="inlineStr"/>
+      <c r="Q105" s="5" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0036</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>TS 708</t>
+        </is>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Steel for the reinforcement of concrete - reinforcing steel</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="n"/>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
+        <is>
+          <t>B500C ribbed bars per TBDY 2018</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="n"/>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P106" s="4" t="inlineStr"/>
+      <c r="Q106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0037</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>TS EN 197-1</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Cement - composition, specifications and conformity criteria for common cements</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Cement types for XS / XA exposure</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P107" s="4" t="inlineStr"/>
+      <c r="Q107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0049</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>API 682 / ISO 21049</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Pumps - Shaft sealing systems for centrifugal and rotary pumps</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical seals for pumps in LDO, ammonia and hazardous service</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="n"/>
+      <c r="M108" s="5" t="n"/>
+      <c r="N108" s="5" t="n"/>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P108" s="4" t="inlineStr"/>
+      <c r="Q108" s="5" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0038</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>ASHRAE 62.1 / 55 / 90.1</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Ventilation for acceptable indoor air quality; thermal comfort; energy standard for buildings</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="n"/>
+      <c r="I109" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>HVAC design method and ventilation rates (HV-DBR-0001)</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="n"/>
+      <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P109" s="4" t="inlineStr"/>
+      <c r="Q109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0057</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>ASME B16.47</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Large Diameter Steel Flanges NPS 26 through NPS 60</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="n"/>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>Flanges of large diameter piping (CW, condensate, bypass steam)</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P110" s="4" t="inlineStr"/>
+      <c r="Q110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0028</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>ASME PTC 19.3 TW</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Thermowells</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="n"/>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>Thermowell wake frequency check (IC-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="n"/>
+      <c r="M111" s="5" t="n"/>
+      <c r="N111" s="5" t="n"/>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P111" s="4" t="inlineStr"/>
+      <c r="Q111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0061</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>ASTM A923 / ASTM G48</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Detecting detrimental intermetallic phase in duplex stainless steels; pitting and crevice corrosion resistance tests</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="n"/>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>Super duplex acceptance tests in the materials report</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="5" t="n"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P112" s="4" t="inlineStr"/>
+      <c r="Q112" s="5" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0022</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>EEMUA 191 / IEC 62682 / ANSI-ISA-18.2</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Alarm systems - design, management and procurement</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="n"/>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>Alarm management (IC-DBR s.12); named in TQ-026</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P113" s="4" t="inlineStr"/>
+      <c r="Q113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0035</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>EN 10025</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Hot rolled products of structural steels</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
+        <is>
+          <t>Steel grades S355J2 / S275JR</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P114" s="4" t="inlineStr"/>
+      <c r="Q114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0034</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>EN 1090-2</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Execution of steel structures and aluminium structures - technical requirements</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>Execution class EXC3 for power block steelwork (ER-13.03)</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="5" t="n"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P115" s="4" t="inlineStr"/>
+      <c r="Q115" s="5" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0016</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>EN 12464-1 / EN 12464-2 / EN 1838</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Lighting of work places (indoor, outdoor) and emergency lighting</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="n"/>
+      <c r="I116" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>Illuminance criteria (EL-DBR s.14)</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="n"/>
+      <c r="M116" s="5" t="n"/>
+      <c r="N116" s="5" t="n"/>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P116" s="4" t="inlineStr"/>
+      <c r="Q116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0050</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>EN 13445</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Unfired pressure vessels (all parts)</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>Pressure vessel design code alternative to ASME VIII</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="5" t="n"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P117" s="4" t="inlineStr"/>
+      <c r="Q117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0039</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>EN 16798-1</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Energy performance of buildings - ventilation for buildings - indoor environmental input parameters</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>Indoor conditions and ventilation rates</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="5" t="n"/>
+      <c r="N118" s="5" t="n"/>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P118" s="4" t="inlineStr"/>
+      <c r="Q118" s="5" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0033</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>EN 1991-1-4 (and -1-1, -1-3, -3)</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Eurocode 1 - Actions on structures: wind, imposed, snow, cranes</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>Wind, snow, imposed and crane loads; only EN 1990 is registered as 'with EN 1991 actions'</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="n"/>
+      <c r="M119" s="5" t="n"/>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P119" s="4" t="inlineStr"/>
+      <c r="Q119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0031</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>EN 1997-1</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Eurocode 7 - Geotechnical design - General rules</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Pile and shallow foundation design, bearing capacity, settlement (CV-DBR-0001 sections 4, 13)</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="5" t="n"/>
+      <c r="N120" s="5" t="n"/>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P120" s="4" t="inlineStr"/>
+      <c r="Q120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0032</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>EN 206</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Concrete - Specification, performance, production and conformity</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>Exposure classes XS / XA, cement types and w/c limits for the marine environment (ER-13.04)</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="5" t="n"/>
+      <c r="N121" s="5" t="n"/>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P121" s="4" t="inlineStr"/>
+      <c r="Q121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0013</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>EN 50272-2</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Safety requirements for secondary batteries - stationary batteries</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>Battery room ventilation (EL-DBR s.9, s.13)</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="5" t="n"/>
+      <c r="N122" s="5" t="n"/>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P122" s="4" t="inlineStr"/>
+      <c r="Q122" s="5" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0040</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>EN ISO 16890</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Air filters for general ventilation</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="inlineStr">
+        <is>
+          <t>Filter classes G4 / F7 / F9 for salt and dust filtration</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="n"/>
+      <c r="M123" s="5" t="n"/>
+      <c r="N123" s="5" t="n"/>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P123" s="4" t="inlineStr"/>
+      <c r="Q123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0017</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60034-30-1</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Rotating electrical machines - efficiency classes (IE code)</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="n"/>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="inlineStr">
+        <is>
+          <t>Motor efficiency (EL-DBR s.8)</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P124" s="4" t="inlineStr"/>
+      <c r="Q124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0019</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60068-3-3 / IEEE 344</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Seismic test methods / seismic qualification of equipment</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="n"/>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="inlineStr">
+        <is>
+          <t>Equipment qualification for PGA 0.45 g (EL-DBR s.3)</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="5" t="n"/>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P125" s="4" t="inlineStr"/>
+      <c r="Q125" s="5" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0003</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n"/>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60071-1/-2</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Insulation co-ordination</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="n"/>
+      <c r="I126" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="inlineStr">
+        <is>
+          <t>Insulation levels and study EL-STU-0005 (EL-DBR s.15-16)</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="n"/>
+      <c r="M126" s="5" t="n"/>
+      <c r="N126" s="5" t="n"/>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P126" s="4" t="inlineStr"/>
+      <c r="Q126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0012</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60079-0, IEC 60079-14, IEC 60079-17</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Explosive atmospheres: equipment general requirements, installation, inspection</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>Hazardous area equipment (EL-DBR s.13)</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="5" t="n"/>
+      <c r="N127" s="5" t="n"/>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P127" s="4" t="inlineStr"/>
+      <c r="Q127" s="5" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0006</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60287</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Electric cables - calculation of the current rating</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>Cable derating (EL-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P128" s="4" t="inlineStr"/>
+      <c r="Q128" s="5" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0005</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60332-3, IEC 60754, IEC 61034, IEC 60331</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Cable fire tests: flame spread, halogen content, smoke density, circuit integrity</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="n"/>
+      <c r="I129" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>ER-11.08 fire performance (EL-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="n"/>
+      <c r="M129" s="5" t="n"/>
+      <c r="N129" s="5" t="n"/>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P129" s="4" t="inlineStr"/>
+      <c r="Q129" s="5" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0004</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60502</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Power cables with extruded insulation for 1 kV to 30 kV</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="n"/>
+      <c r="I130" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="inlineStr">
+        <is>
+          <t>Cable criteria (EL-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="n"/>
+      <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P130" s="4" t="inlineStr"/>
+      <c r="Q130" s="5" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0024</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60529</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Degrees of protection provided by enclosures (IP code)</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="n"/>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>Instrument and cabinet ingress protection (IC-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="n"/>
+      <c r="M131" s="5" t="n"/>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P131" s="4" t="inlineStr"/>
+      <c r="Q131" s="5" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0020</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60534 (parts 2-1, 4, 8-3, 8-4)</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Industrial-process control valves: sizing, leakage, noise</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="n"/>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>Control valve criteria (IC-DBR s.11)</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="n"/>
+      <c r="M132" s="5" t="n"/>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P132" s="4" t="inlineStr"/>
+      <c r="Q132" s="5" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0025</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60751 / IEC 60584</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Industrial platinum resistance thermometers / thermocouples</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="n"/>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>Temperature sensors (IC-DBR s.9)</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="n"/>
+      <c r="M133" s="5" t="n"/>
+      <c r="N133" s="5" t="n"/>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P133" s="4" t="inlineStr"/>
+      <c r="Q133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0009</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60870-5-104</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Telecontrol equipment - network access</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>RTU to dispatch centre (EL-DBR s.11)</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="n"/>
+      <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P134" s="4" t="inlineStr"/>
+      <c r="Q134" s="5" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0015</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>IEC 60896-21/-22</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Stationary lead-acid batteries - valve regulated</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>Battery selection (EL-DBR s.9)</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="5" t="n"/>
+      <c r="N135" s="5" t="n"/>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P135" s="4" t="inlineStr"/>
+      <c r="Q135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0018</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>IEC 61000-2-4 / IEC 61000-6-2 / IEC 61000-6-4</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>EMC: compatibility levels in industrial plants, immunity and emission standards</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="n"/>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>Harmonics limit (EL-DBR s.8, s.16) and DCS EMC (IC-DBR s.9)</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P136" s="4" t="inlineStr"/>
+      <c r="Q136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0002</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>IEC 61439</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Low-voltage switchgear and controlgear assemblies</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="n"/>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>LV boards and MCCs (EL-DBR s.4)</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="5" t="n"/>
+      <c r="N137" s="5" t="n"/>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P137" s="4" t="inlineStr"/>
+      <c r="Q137" s="5" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0021</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>IEC 61508</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Functional safety of E/E/PE safety-related systems</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="n"/>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>SIL certification of SIS devices (IC-DBR s.8, s.10)</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="n"/>
+      <c r="M138" s="5" t="n"/>
+      <c r="N138" s="5" t="n"/>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P138" s="4" t="inlineStr"/>
+      <c r="Q138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0008</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>IEC 61869</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Instrument transformers</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="n"/>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>Metering and protection CT/VT (EL-DBR s.11)</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="n"/>
+      <c r="M139" s="5" t="n"/>
+      <c r="N139" s="5" t="n"/>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P139" s="4" t="inlineStr"/>
+      <c r="Q139" s="5" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0001</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>IEC 62271-200</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>AC metal-enclosed switchgear and controlgear for rated voltages above 1 kV up to and including 52 kV</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>MV switchgear type test and internal arc classification (EL-DBR s.4, s.11)</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="5" t="n"/>
+      <c r="N140" s="5" t="n"/>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P140" s="4" t="inlineStr"/>
+      <c r="Q140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0007</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>IEC 62439-3</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Industrial networks - PRP and HSR</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>Redundant IEC 61850 station bus (EL-DBR s.11)</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="n"/>
+      <c r="M141" s="5" t="n"/>
+      <c r="N141" s="5" t="n"/>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P141" s="4" t="inlineStr"/>
+      <c r="Q141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0023</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>IEC 62541 (OPC UA)</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>OPC Unified Architecture</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="n"/>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>TCS to DCS integration (IC-DBR s.5)</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="5" t="n"/>
+      <c r="N142" s="5" t="n"/>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P142" s="4" t="inlineStr"/>
+      <c r="Q142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0011</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>IEEE 1584</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Guide for performing arc-flash hazard calculations</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>Arc-flash study in protection coordination (EL-DBR s.16)</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="n"/>
+      <c r="M143" s="5" t="n"/>
+      <c r="N143" s="5" t="n"/>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P143" s="4" t="inlineStr"/>
+      <c r="Q143" s="5" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0010</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>IEEE C37.238</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>IEEE Standard Profile for use of IEEE 1588 PTP in power system applications</t>
+        </is>
+      </c>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="n"/>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>Time synchronisation of relays (EL-DBR s.11, IC-DBR s.14)</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="n"/>
+      <c r="M144" s="5" t="n"/>
+      <c r="N144" s="5" t="n"/>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P144" s="4" t="inlineStr"/>
+      <c r="Q144" s="5" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0043</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>ISA 71.04</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Environmental conditions for process measurement and control systems: airborne contaminants</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>Gaseous contaminant severity level for control rooms in the coastal atmosphere</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="5" t="n"/>
+      <c r="N145" s="5" t="n"/>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="inlineStr"/>
+      <c r="Q145" s="5" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0063</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>ISO 10816-7</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical vibration - Evaluation of machine vibration by measurements on non-rotating parts - Part 7: Rotodynamic pumps for industrial applications</t>
+        </is>
+      </c>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>mechanical</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>pump vibration acceptance (ME-SPC-0001 section 5)</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="5" t="n"/>
+      <c r="N146" s="5" t="n"/>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P146" s="4" t="inlineStr"/>
+      <c r="Q146" s="5" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0051</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>ISO 12944-1, -3 to -9</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Paints and varnishes - Corrosion protection of steel structures by protective paint systems</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="n"/>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>Only ISO 12944-2 is registered; systems, design, application, inspection parts are cited in the painting specification</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="n"/>
+      <c r="M147" s="5" t="n"/>
+      <c r="N147" s="5" t="n"/>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P147" s="4" t="inlineStr"/>
+      <c r="Q147" s="5" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0062</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E148" s="4" t="inlineStr">
+        <is>
+          <t>ISO 13707 / API 617 / NEMA SM23</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Allowable nozzle loads for rotating equipment</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="n"/>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>Nozzle load check in piping stress analysis</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="n"/>
+      <c r="M148" s="5" t="n"/>
+      <c r="N148" s="5" t="n"/>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="inlineStr"/>
+      <c r="Q148" s="5" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0047</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>ISO 13709 / API 610</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Centrifugal pumps for petroleum, petrochemical and natural gas industries</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="n"/>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>Pump design standard cited in ME-SPC-0001 (only API 650 / ASME B31 etc. are registered)</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="n"/>
+      <c r="M149" s="5" t="n"/>
+      <c r="N149" s="5" t="n"/>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P149" s="4" t="inlineStr"/>
+      <c r="Q149" s="5" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0056</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>ISO 14692 / EN 1796 / AWWA M45</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>GRP piping design and installation</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="n"/>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>Seawater GRP piping design</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P150" s="4" t="inlineStr"/>
+      <c r="Q150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0029</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>ISO 15848-1</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Industrial valves - measurement of fugitive emissions</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="n"/>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>Stem emission of fuel gas valves (IC-DBR s.11)</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="n"/>
+      <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="inlineStr"/>
+      <c r="Q151" s="5" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0054</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>ISO 2063</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Thermal spraying - Zinc, aluminium and their alloys</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="n"/>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>Thermally sprayed aluminium under insulation</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="n"/>
+      <c r="M152" s="5" t="n"/>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P152" s="4" t="inlineStr"/>
+      <c r="Q152" s="5" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0030</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="n"/>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>ISO 20816-3</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Mechanical vibration - evaluation of machine vibration, industrial machines</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="n"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>BOP machine vibration monitoring (IC-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="n"/>
+      <c r="M153" s="5" t="n"/>
+      <c r="N153" s="5" t="n"/>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P153" s="4" t="inlineStr"/>
+      <c r="Q153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0055</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>ISO 3864 / ISO 7010</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Graphical symbols - Safety colours and safety signs</t>
+        </is>
+      </c>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="n"/>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>Safety colours and hazard marking</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="n"/>
+      <c r="M154" s="5" t="n"/>
+      <c r="N154" s="5" t="n"/>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P154" s="4" t="inlineStr"/>
+      <c r="Q154" s="5" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0027</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>ISO 5167</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Measurement of fluid flow by differential pressure devices</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="n"/>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>Flow measurement (IC-DBR s.10)</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="n"/>
+      <c r="M155" s="5" t="n"/>
+      <c r="N155" s="5" t="n"/>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P155" s="4" t="inlineStr"/>
+      <c r="Q155" s="5" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0048</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>ISO 5199</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Technical specifications for centrifugal pumps - Class II</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="n"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>Pump standard for water and utility services in ME-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="n"/>
+      <c r="M156" s="5" t="n"/>
+      <c r="N156" s="5" t="n"/>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P156" s="4" t="inlineStr"/>
+      <c r="Q156" s="5" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0059</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>ISO 5801 / ISO 14694 / ISO 12759</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Fans - performance, balance and vibration, efficiency classification</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="n"/>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Fans in ME-SPC-0001</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="n"/>
+      <c r="M157" s="5" t="n"/>
+      <c r="N157" s="5" t="n"/>
+      <c r="O157" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P157" s="4" t="inlineStr"/>
+      <c r="Q157" s="5" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0052</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>ISO 8501-1 / ISO 8501-3</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Preparation of steel substrates before application of paints - visual assessment of surface cleanliness</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="n"/>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>Sa 2.5 surface preparation</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="n"/>
+      <c r="M158" s="5" t="n"/>
+      <c r="N158" s="5" t="n"/>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P158" s="4" t="inlineStr"/>
+      <c r="Q158" s="5" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0053</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>ISO 8502 / ISO 8503 / ISO 19840</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Surface cleanliness tests, surface profile and DFT measurement</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="n"/>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>Coating inspection methods</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="n"/>
+      <c r="M159" s="5" t="n"/>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P159" s="4" t="inlineStr"/>
+      <c r="Q159" s="5" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0014</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>ISO 8528-1/-5</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Reciprocating IC engine driven AC generating sets</t>
+        </is>
+      </c>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="n"/>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>EDG rating and load-step performance (EL-DBR s.9)</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="n"/>
+      <c r="M160" s="5" t="n"/>
+      <c r="N160" s="5" t="n"/>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P160" s="4" t="inlineStr"/>
+      <c r="Q160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0044</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>ISO 9612</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Acoustics - determination of occupational noise exposure</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="n"/>
+      <c r="I161" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J161" s="5" t="inlineStr">
+        <is>
+          <t>Occupational noise assessment</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="n"/>
+      <c r="M161" s="5" t="n"/>
+      <c r="N161" s="5" t="n"/>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P161" s="4" t="inlineStr"/>
+      <c r="Q161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0060</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="n"/>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>ISO 9906</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Rotodynamic pumps - Hydraulic performance acceptance tests, Grades 1, 2 and 3</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="n"/>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t>Pump performance guarantees</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="n"/>
+      <c r="M162" s="5" t="n"/>
+      <c r="N162" s="5" t="n"/>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P162" s="4" t="inlineStr"/>
+      <c r="Q162" s="5" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0026</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>NAMUR NE43 / NE107</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Signal level for failure information / self-monitoring and diagnosis of field devices</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="n"/>
+      <c r="I163" s="5" t="inlineStr">
+        <is>
+          <t>electrical
+i_and_c</t>
+        </is>
+      </c>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t>4-20 mA HART fault signals and device status (IC-DBR s.9)</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="n"/>
+      <c r="M163" s="5" t="n"/>
+      <c r="N163" s="5" t="n"/>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P163" s="4" t="inlineStr"/>
+      <c r="Q163" s="5" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0046</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>NFPA 101</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Life Safety Code</t>
+        </is>
+      </c>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="n"/>
+      <c r="I164" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>Escape route criteria complementary to the Fire Regulation</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="n"/>
+      <c r="M164" s="5" t="n"/>
+      <c r="N164" s="5" t="n"/>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P164" s="4" t="inlineStr"/>
+      <c r="Q164" s="5" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0042</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>NFPA 15 / NFPA 24 / NFPA 13</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Water spray fixed systems; private fire service mains; sprinkler systems</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="n"/>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t>Transformer deluge, ring main and hydrants, building sprinklers</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="n"/>
+      <c r="M165" s="5" t="n"/>
+      <c r="N165" s="5" t="n"/>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P165" s="4" t="inlineStr"/>
+      <c r="Q165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0041</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>NFPA 90A</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>Standard for the installation of air-conditioning and ventilating systems</t>
+        </is>
+      </c>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="n"/>
+      <c r="I166" s="5" t="inlineStr">
+        <is>
+          <t>civil
+hvac
+hse</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t>Fire dampers, smoke shutdown of AHUs</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="n"/>
+      <c r="M166" s="5" t="n"/>
+      <c r="N166" s="5" t="n"/>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P166" s="4" t="inlineStr"/>
+      <c r="Q166" s="5" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>REF-EPCE-0058</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>TEMA</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Standards of the Tubular Exchanger Manufacturers Association</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>edition at Base Date</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="n"/>
+      <c r="I167" s="5" t="inlineStr">
+        <is>
+          <t>mechanical
+piping</t>
+        </is>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
+        <is>
+          <t>Shell-and-tube exchanger design</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>Istanbul EPC</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="n"/>
+      <c r="M167" s="5" t="n"/>
+      <c r="N167" s="5" t="n"/>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P167" s="4" t="inlineStr"/>
+      <c r="Q167" s="5" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q4"/>
@@ -8429,7 +12232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T03:51:00Z by EPCE | data e9668cfc01fd011a</t>
         </is>
       </c>
     </row>
@@ -10690,7 +14493,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T03:51:00Z by EPCE | data e9668cfc01fd011a</t>
         </is>
       </c>
     </row>
@@ -11148,7 +14951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11167,7 +14970,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine standards_register v1.0.0 | generated 2026-09-29T02:55:43Z by SETUP | data 4d33db05aa4b48e7</t>
+          <t>engine standards_register v1.0.0 | generated 2026-09-29T03:51:00Z by EPCE | data e9668cfc01fd011a</t>
         </is>
       </c>
     </row>
@@ -14430,29 +18233,29 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>PMT-001</t>
+          <t>REF-EPCE-0049</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Law 2872, EIA Regulation</t>
+          <t>API 682 / ISO 21049: status proposed</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>PMT-001</t>
+          <t>REF-EPCE-0038</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -14460,43 +18263,43 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>ASHRAE 62.1 / 55 / 90.1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>PMT-002</t>
+          <t>REF-EPCE-0057</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Law 6446</t>
+          <t>ASME B16.47: status proposed</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>PMT-002</t>
+          <t>REF-EPCE-0028</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
@@ -14504,43 +18307,43 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>ASME PTC 19.3 TW: status proposed</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>PMT-003</t>
+          <t>REF-EPCE-0061</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Law 6446, Grid Code</t>
+          <t>ASTM A923 / ASTM G48: status proposed</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>PMT-003</t>
+          <t>REF-EPCE-0022</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
@@ -14548,65 +18351,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>EEMUA 191 / IEC 62682 / ANSI-ISA-18.2: status proposed</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>PMT-004</t>
+          <t>REF-EPCE-0035</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Law 6446, Grid Code</t>
+          <t>EN 10025: status proposed</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>PMT-004</t>
+          <t>REF-EPCE-0034</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-03-15 + 90 d = 2028-06-13; needed 2028-07-15: float 32 d</t>
+          <t>EN 1090-2: status proposed</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>PMT-004</t>
+          <t>REF-EPCE-0016</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -14614,65 +18417,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>EN 12464-1 / EN 12464-2 / EN 1838: status proposed</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>PMT-005</t>
+          <t>REF-EPCE-0050</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Law 3194, TBDY 2018, Fire Regulation</t>
+          <t>EN 13445: status proposed</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>PMT-005</t>
+          <t>REF-EPCE-0039</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+          <t>EN 16798-1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>PMT-005</t>
+          <t>REF-EPCE-0033</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -14680,65 +18483,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>EN 1991-1-4 (and -1-1, -1-3, -3): status proposed</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>PMT-006</t>
+          <t>REF-EPCE-0031</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Law 3621, EIA Regulation</t>
+          <t>EN 1997-1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>PMT-006</t>
+          <t>REF-EPCE-0032</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-02 + 180 d = 2027-05-01; needed 2027-10-01: float 153 d</t>
+          <t>EN 206: status proposed</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>PMT-006</t>
+          <t>REF-EPCE-0013</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -14746,65 +18549,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>EN 50272-2: status proposed</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>PMT-007</t>
+          <t>REF-EPCE-0040</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Law 3621</t>
+          <t>EN ISO 16890: status proposed</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>PMT-007</t>
+          <t>REF-EPCE-0017</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-04-01 + 180 d = 2027-09-28; needed 2027-11-01: float 34 d</t>
+          <t>IEC 60034-30-1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>PMT-007</t>
+          <t>REF-EPCE-0019</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -14812,65 +18615,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>IEC 60068-3-3 / IEEE 344: status proposed</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>PMT-008</t>
+          <t>REF-EPCE-0003</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Law 3621</t>
+          <t>IEC 60071-1/-2: status proposed</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>PMT-008</t>
+          <t>REF-EPCE-0012</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-15 + 30 d = 2027-10-15; needed 2027-11-01: float 17 d</t>
+          <t>IEC 60079-0, IEC 60079-14, IEC 60079-17: status proposed</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>PMT-008</t>
+          <t>REF-EPCE-0006</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
@@ -14878,65 +18681,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60287: status proposed</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>PMT-009</t>
+          <t>REF-EPCE-0005</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Law 2918</t>
+          <t>IEC 60332-3, IEC 60754, IEC 61034, IEC 60331: status proposed</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>PMT-009</t>
+          <t>REF-EPCE-0004</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-01 + 30 d = 2027-10-01; needed 2027-11-01: float 31 d</t>
+          <t>IEC 60502: status proposed</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>PMT-009</t>
+          <t>REF-EPCE-0024</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
@@ -14944,65 +18747,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>IEC 60529: status proposed</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>PMT-010</t>
+          <t>REF-EPCE-0020</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Law 6331, Construction OHS Regulation</t>
+          <t>IEC 60534 (parts 2-1, 4, 8-3, 8-4): status proposed</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>PMT-010</t>
+          <t>REF-EPCE-0025</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-02 + 10 d = 2026-11-12; needed 2026-11-16: float 4 d</t>
+          <t>IEC 60751 / IEC 60584: status proposed</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>PMT-010</t>
+          <t>REF-EPCE-0009</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -15010,65 +18813,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>IEC 60870-5-104: status proposed</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>PMT-011</t>
+          <t>REF-EPCE-0015</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Noise Regulation, EIA Regulation</t>
+          <t>IEC 60896-21/-22: status proposed</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>PMT-011</t>
+          <t>REF-EPCE-0018</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C180" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-12-01 + 30 d = 2026-12-31; needed 2027-01-15: float 15 d</t>
+          <t>IEC 61000-2-4 / IEC 61000-6-2 / IEC 61000-6-4: status proposed</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>PMT-011</t>
+          <t>REF-EPCE-0002</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -15076,65 +18879,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>IEC 61439: status proposed</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>PMT-012</t>
+          <t>REF-EPCE-0021</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Law 167</t>
+          <t>IEC 61508: status proposed</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>PMT-012</t>
+          <t>REF-EPCE-0008</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C183" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+          <t>IEC 61869: status proposed</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>PMT-012</t>
+          <t>REF-EPCE-0001</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -15142,65 +18945,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>IEC 62271-200: status proposed</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>PMT-013</t>
+          <t>REF-EPCE-0007</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C185" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Law 7381</t>
+          <t>IEC 62439-3: status proposed</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>PMT-013</t>
+          <t>REF-EPCE-0023</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>apply 2027-09-15 + 60 d = 2027-11-14; needed 2027-12-01: float 17 d</t>
+          <t>IEC 62541 (OPC UA): status proposed</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>PMT-013</t>
+          <t>REF-EPCE-0011</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -15208,65 +19011,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C187" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>IEEE 1584: status proposed</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>PMT-014</t>
+          <t>REF-EPCE-0010</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Law 4646</t>
+          <t>IEEE C37.238: status proposed</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>PMT-014</t>
+          <t>REF-EPCE-0043</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-03-15 + 120 d = 2028-07-13; needed 2028-08-15: float 33 d</t>
+          <t>ISA 71.04: status proposed</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>PMT-014</t>
+          <t>REF-EPCE-0063</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -15274,65 +19077,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 10816-7: status proposed</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>PMT-015</t>
+          <t>REF-EPCE-0051</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Major Accident Regulation</t>
+          <t>ISO 12944-1, -3 to -9: status proposed</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>PMT-015</t>
+          <t>REF-EPCE-0062</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C192" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-08-15 + 60 d = 2028-10-14; needed 2028-11-01: float 18 d</t>
+          <t>ISO 13707 / API 617 / NEMA SM23: status proposed</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>PMT-015</t>
+          <t>REF-EPCE-0047</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -15340,65 +19143,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C193" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 13709 / API 610: status proposed</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>PMT-016</t>
+          <t>REF-EPCE-0056</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Work Equipment Regulation, PED 2014/68/EU</t>
+          <t>ISO 14692 / EN 1796 / AWWA M45: status proposed</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>PMT-016</t>
+          <t>REF-EPCE-0029</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C195" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-06-15 + 14 d = 2028-06-29; needed 2028-08-01: float 33 d</t>
+          <t>ISO 15848-1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>PMT-016</t>
+          <t>REF-EPCE-0054</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
@@ -15406,65 +19209,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 2063: status proposed</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>PMT-017</t>
+          <t>REF-EPCE-0030</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, SKHKKY</t>
+          <t>ISO 20816-3: status proposed</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>PMT-017</t>
+          <t>REF-EPCE-0055</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-07-15 + 45 d = 2028-08-29; needed 2028-10-02: float 34 d</t>
+          <t>ISO 3864 / ISO 7010: status proposed</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>PMT-017</t>
+          <t>REF-EPCE-0027</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
@@ -15472,65 +19275,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C199" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>ISO 5167: status proposed</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>PMT-018</t>
+          <t>REF-EPCE-0048</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+          <t>ISO 5199: status proposed</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>PMT-018</t>
+          <t>REF-EPCE-0059</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C201" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>apply 2028-08-15 + 30 d = 2028-09-14; needed 2028-10-02: float 18 d</t>
+          <t>ISO 5801 / ISO 14694 / ISO 12759: status proposed</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>PMT-018</t>
+          <t>REF-EPCE-0052</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
@@ -15538,65 +19341,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C202" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>ISO 8501-1 / ISO 8501-3: status proposed</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>PMT-019</t>
+          <t>REF-EPCE-0053</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C203" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+          <t>ISO 8502 / ISO 8503 / ISO 19840: status proposed</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>PMT-019</t>
+          <t>REF-EPCE-0014</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C204" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-03-01 + 90 d = 2029-05-30; needed 2029-07-04: float 35 d</t>
+          <t>ISO 8528-1/-5: status proposed</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>PMT-019</t>
+          <t>REF-EPCE-0044</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
@@ -15604,65 +19407,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C205" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>ISO 9612: status proposed</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>PMT-020</t>
+          <t>REF-EPCE-0060</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C206" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Law 3194, Fire Regulation</t>
+          <t>ISO 9906: status proposed</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>PMT-020</t>
+          <t>REF-EPCE-0026</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C207" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-05-15 + 30 d = 2029-06-14; needed 2029-07-04: float 20 d</t>
+          <t>NAMUR NE43 / NE107: status proposed</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>PMT-020</t>
+          <t>REF-EPCE-0046</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -15670,65 +19473,65 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>NFPA 101: status proposed</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>PMT-021</t>
+          <t>REF-EPCE-0042</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C209" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Grid Code</t>
+          <t>NFPA 15 / NFPA 24 / NFPA 13: status proposed</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>PMT-021</t>
+          <t>REF-EPCE-0041</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C210" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>apply 2029-01-02 + 60 d = 2029-03-03; needed 2029-07-04: float 123 d</t>
+          <t>NFPA 90A: status proposed</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>PMT-021</t>
+          <t>REF-EPCE-0058</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -15736,43 +19539,43 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEC, IEPC, OWNER</t>
+          <t>TEMA: status proposed</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>PMT-022</t>
+          <t>REF-EPCE-0036</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C212" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>WPCR</t>
+          <t>TS 708: status proposed</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>PMT-022</t>
+          <t>REF-EPCE-0037</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -15780,70 +19583,70 @@
           <t>agreement</t>
         </is>
       </c>
-      <c r="C213" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>TS EN 197-1: status proposed</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>PMT-023</t>
+          <t>REF-EPCE-0045</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
-        </is>
-      </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>authority</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Law 6446</t>
+          <t>Turkish regulations on noise at work and on chemical agents at work: regulation without enforcing authority</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>PMT-023</t>
+          <t>REF-EPCE-0045</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C215" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>apply 2026-12-15 + 60 d = 2027-02-13; needed 2027-03-15: float 30 d</t>
+          <t>Turkish regulations on noise at work and on chemical agents at work: status proposed</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>PMT-023</t>
+          <t>PMT-001</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>legal basis</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -15853,19 +19656,19 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>agreed by IEPC, OWNER</t>
+          <t>Law 2872, EIA Regulation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>PMT-025</t>
+          <t>PMT-001</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>legal basis</t>
+          <t>agreement</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -15875,49 +19678,1457 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Law 2863</t>
+          <t>agreed by IEPC, OWNER</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>PMT-025</t>
+          <t>PMT-002</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>timing</t>
-        </is>
-      </c>
-      <c r="C218" s="7" t="inlineStr">
-        <is>
-          <t>INFO</t>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>no lead time: procedural, needed from 2026-11-16</t>
+          <t>Law 6446</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
+          <t>PMT-002</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>PMT-003</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>Law 6446, Grid Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>PMT-003</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>PMT-004</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>Law 6446, Grid Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>PMT-004</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-03-15 + 90 d = 2028-06-13; needed 2028-07-15: float 32 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>PMT-004</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>PMT-005</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Law 3194, TBDY 2018, Fire Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>PMT-005</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>PMT-005</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>PMT-006</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>Law 3621, EIA Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>PMT-006</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-11-02 + 180 d = 2027-05-01; needed 2027-10-01: float 153 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>PMT-006</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>PMT-007</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Law 3621</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>PMT-007</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>apply 2027-04-01 + 180 d = 2027-09-28; needed 2027-11-01: float 34 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>PMT-007</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>PMT-008</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>Law 3621</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>PMT-008</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>apply 2027-09-15 + 30 d = 2027-10-15; needed 2027-11-01: float 17 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>PMT-008</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>PMT-009</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Law 2918</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>PMT-009</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>apply 2027-09-01 + 30 d = 2027-10-01; needed 2027-11-01: float 31 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>PMT-009</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>PMT-010</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>Law 6331, Construction OHS Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>PMT-010</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-11-02 + 10 d = 2026-11-12; needed 2026-11-16: float 4 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>PMT-010</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>PMT-011</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>Noise Regulation, EIA Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>PMT-011</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-12-01 + 30 d = 2026-12-31; needed 2027-01-15: float 15 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>PMT-011</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>PMT-012</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>Law 167</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>PMT-012</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-11-16 + 60 d = 2027-01-15; needed 2027-02-15: float 31 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>PMT-012</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>PMT-013</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>Law 7381</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>PMT-013</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>apply 2027-09-15 + 60 d = 2027-11-14; needed 2027-12-01: float 17 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>PMT-013</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>PMT-014</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>Law 4646</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>PMT-014</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-03-15 + 120 d = 2028-07-13; needed 2028-08-15: float 33 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>PMT-014</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>PMT-015</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C255" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>Major Accident Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>PMT-015</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-08-15 + 60 d = 2028-10-14; needed 2028-11-01: float 18 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>PMT-015</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C257" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>PMT-016</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C258" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>Work Equipment Regulation, PED 2014/68/EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>PMT-016</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D259" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-06-15 + 14 d = 2028-06-29; needed 2028-08-01: float 33 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>PMT-016</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>PMT-017</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>Env. Permit Regulation, SKHKKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>PMT-017</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-07-15 + 45 d = 2028-08-29; needed 2028-10-02: float 34 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>PMT-017</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>PMT-018</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>PMT-018</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>apply 2028-08-15 + 30 d = 2028-09-14; needed 2028-10-02: float 18 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>PMT-018</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>PMT-019</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>Env. Permit Regulation, LCP Regulation, WPCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>PMT-019</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>apply 2029-03-01 + 90 d = 2029-05-30; needed 2029-07-04: float 35 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>PMT-019</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>PMT-020</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>Law 3194, Fire Regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>PMT-020</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>apply 2029-05-15 + 30 d = 2029-06-14; needed 2029-07-04: float 20 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>PMT-020</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C272" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>PMT-021</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C273" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>Grid Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>PMT-021</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>apply 2029-01-02 + 60 d = 2029-03-03; needed 2029-07-04: float 123 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>PMT-021</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C275" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEC, IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>PMT-022</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C276" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>WPCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>PMT-022</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C277" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>PMT-023</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>Law 6446</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>PMT-023</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C279" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>apply 2026-12-15 + 60 d = 2027-02-13; needed 2027-03-15: float 30 d</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>PMT-023</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+      <c r="C280" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>agreed by IEPC, OWNER</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
           <t>PMT-025</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>legal basis</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>Law 2863</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>PMT-025</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>no lead time: procedural, needed from 2026-11-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>PMT-025</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
         <is>
           <t>agreement</t>
         </is>
       </c>
-      <c r="C219" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D219" s="5" t="inlineStr">
+      <c r="C283" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
         <is>
           <t>agreed by IEPC, OWNER</t>
         </is>
